--- a/week-04/overall marketshare with competitors.xlsx
+++ b/week-04/overall marketshare with competitors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192FB174-6377-41CC-AC1A-E6E2AE8B4B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C81B19-1814-4E6E-939B-D33AAE1A72C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12C91C7C-56FE-4FB1-92D7-331A5E47D64E}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
   <si>
     <t>vendor_group</t>
   </si>
@@ -578,7 +578,11 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -589,6 +593,909 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'data-1777492718949'!$B$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>overall_market_share_pct</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-CAC9-42DC-BEAD-80A48821B2C9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data-1777492718949'!$A$12:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Others</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Diageo Americas</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pernod Ricard</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Luxco</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bacardi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data-1777492718949'!$B$12:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>59.09</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.48</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.84</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CAC9-42DC-BEAD-80A48821B2C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="55"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{053F6896-0313-2EED-30B4-356A06DDB71E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AD864552-C017-4048-A31D-A2D56F313CA6}" name="Table1" displayName="Table1" ref="A1:C6" totalsRowShown="0">
+  <autoFilter ref="A1:C6" xr:uid="{AD864552-C017-4048-A31D-A2D56F313CA6}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C0416897-791C-408A-8878-D485D729AD3B}" name="vendor_group"/>
+    <tableColumn id="2" xr3:uid="{36510C00-F1AE-42F5-9E96-FD7640FAC2E2}" name="total_revenue" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{A962A342-752F-4CB1-A5E7-8776A4E2AC8B}" name="overall_market_share_pct"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -908,12 +1815,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D2689A-D4CA-4478-891F-C9FBD277BF3B}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -982,7 +1889,59 @@
         <v>5.41</v>
       </c>
     </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>59.09</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>21.48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>5.41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/week-04/overall marketshare with competitors.xlsx
+++ b/week-04/overall marketshare with competitors.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onurkaraer\Documents\DataAnalytics\week-04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C81B19-1814-4E6E-939B-D33AAE1A72C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07D98AAC-8150-476C-8A82-25505D24545C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{12C91C7C-56FE-4FB1-92D7-331A5E47D64E}"/>
   </bookViews>
   <sheets>
     <sheet name="data-1777492718949" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>vendor_group</t>
   </si>
@@ -44,6 +57,9 @@
   </si>
   <si>
     <t>Bacardi</t>
+  </si>
+  <si>
+    <t>Rest of Market</t>
   </si>
 </sst>
 </file>
@@ -672,6 +688,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2172-4082-889F-FA5C7FD328E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -687,6 +708,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2172-4082-889F-FA5C7FD328E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -702,6 +728,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2172-4082-889F-FA5C7FD328E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -717,6 +748,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2172-4082-889F-FA5C7FD328E6}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -886,7 +922,259 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'data-1777492718949'!$A$16:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bacardi</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Rest of Market</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'data-1777492718949'!$B$16:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>5.41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>94.59</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A858-4821-8383-F7A6B6800617}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1445,6 +1733,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1478,6 +2285,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F146D10-1E6F-D2FC-4FCE-5E7FC7C7136F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1815,7 +2658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D2689A-D4CA-4478-891F-C9FBD277BF3B}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -1937,6 +2780,15 @@
         <v>5.41</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <f>SUM(B12:B15)</f>
+        <v>94.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
